--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E - PRIVATE LAND ONLY ARCHERY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E - PRIVATE LAND ONLY ARCHERY.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -645,7 +650,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -702,7 +708,8 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -755,7 +762,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -808,7 +816,8 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -861,7 +870,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -914,7 +924,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -967,7 +978,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1020,7 +1032,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1073,7 +1086,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1126,7 +1140,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1179,7 +1194,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1232,7 +1248,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1285,7 +1302,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1338,7 +1356,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1391,7 +1410,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1448,7 +1468,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1496,8 +1517,13 @@
       </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1545,8 +1571,13 @@
       </c>
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1594,8 +1625,13 @@
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1648,7 +1684,8 @@
           <t>7.4</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1701,7 +1738,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1754,7 +1792,8 @@
           <t>6.6</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1807,7 +1846,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1855,8 +1895,13 @@
       </c>
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1904,8 +1949,13 @@
       </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -1953,8 +2003,13 @@
       </c>
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2002,8 +2057,13 @@
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -2051,8 +2111,13 @@
       </c>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2100,8 +2165,13 @@
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -2149,8 +2219,13 @@
       </c>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -2203,7 +2278,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -2256,7 +2332,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -2309,7 +2386,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -2362,7 +2440,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -2415,7 +2494,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -2463,8 +2543,13 @@
       </c>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -2512,8 +2597,13 @@
       </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -2566,7 +2656,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2619,7 +2710,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -2667,8 +2759,13 @@
       </c>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2721,7 +2818,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -2769,8 +2867,13 @@
       </c>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O43"/>
